--- a/Result/checksun_type/光學.xlsx
+++ b/Result/checksun_type/光學.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1648,17 +1648,17 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1668,37 +1668,37 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1893,11 +1893,15 @@
           <t>80.22999999999999</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>79.68000000000001</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>74.63</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>79.68</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>74.63</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2013,7 +2017,7 @@
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR2" t="inlineStr">
@@ -2630,17 +2634,17 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -2650,37 +2654,37 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -2875,11 +2879,15 @@
           <t>79.84</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>74.34999999999999</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>74.35</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -2995,7 +3003,7 @@
       </c>
       <c r="DQ3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR3" t="inlineStr">
@@ -3607,62 +3615,62 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3857,11 +3865,15 @@
           <t>79.13000000000001</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>79.66</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>74.05</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>79.66</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>74.05</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -3977,7 +3989,7 @@
       </c>
       <c r="DQ4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR4" t="inlineStr">
@@ -4589,62 +4601,62 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -4839,11 +4851,15 @@
           <t>78.61</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>79.55</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>73.72</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>79.55</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>73.72</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -5596,7 +5612,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -5606,27 +5622,27 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -5821,11 +5837,15 @@
           <t>78.46000000000001</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>79.31999999999999</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>73.48</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>79.32</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>73.48</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6578,37 +6598,37 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -6803,11 +6823,15 @@
           <t>78.57000000000001</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>79.15000000000001</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>73.42</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>79.15</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>73.42</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7560,37 +7584,37 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -7785,11 +7809,15 @@
           <t>78.68</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>78.98</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>73.42</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>78.98</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>73.42</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8532,7 +8560,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -8542,37 +8570,37 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8767,11 +8795,15 @@
           <t>78.72</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>78.58</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>73.45</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>78.58</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>73.45</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9514,47 +9546,47 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9749,11 +9781,15 @@
           <t>78.72</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>78.01000000000001</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>73.52</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>78.01</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>73.52</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
@@ -10486,17 +10522,17 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -10506,37 +10542,37 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -10731,11 +10767,15 @@
           <t>26.53</t>
         </is>
       </c>
-      <c r="CQ11" t="n">
-        <v>26.58</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>26.2</v>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>26.58</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>26.2</t>
+        </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
@@ -11463,62 +11503,62 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -11713,11 +11753,15 @@
           <t>26.45</t>
         </is>
       </c>
-      <c r="CQ12" t="n">
-        <v>26.59</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>26.18</v>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>26.59</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>26.18</t>
+        </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
@@ -12455,12 +12499,12 @@
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -12470,37 +12514,37 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -12695,11 +12739,15 @@
           <t>26.335</t>
         </is>
       </c>
-      <c r="CQ13" t="n">
-        <v>26.55</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>26.15</v>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>26.55</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>26.15</t>
+        </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
@@ -13432,17 +13480,17 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -13452,37 +13500,37 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AW14" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AY14" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -13677,11 +13725,15 @@
           <t>26.225</t>
         </is>
       </c>
-      <c r="CQ14" t="n">
-        <v>26.52</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>26.11</v>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>26.52</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>26.11</t>
+        </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
@@ -14414,17 +14466,17 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -14434,37 +14486,37 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -14659,11 +14711,15 @@
           <t>26.17</t>
         </is>
       </c>
-      <c r="CQ15" t="n">
-        <v>26.51</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>26.09</v>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>26.51</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>26.09</t>
+        </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
@@ -15391,62 +15447,62 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -15641,11 +15697,15 @@
           <t>26.12</t>
         </is>
       </c>
-      <c r="CQ16" t="n">
-        <v>26.51</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>26.08</v>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>26.51</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>26.08</t>
+        </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
@@ -16398,7 +16458,7 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -16413,22 +16473,22 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -16623,11 +16683,15 @@
           <t>26.085</t>
         </is>
       </c>
-      <c r="CQ17" t="n">
-        <v>26.48</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>26.08</v>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>26.48</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>26.08</t>
+        </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
@@ -17380,7 +17444,7 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -17395,22 +17459,22 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -17605,11 +17669,15 @@
           <t>26.145</t>
         </is>
       </c>
-      <c r="CQ18" t="n">
-        <v>26.45</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>26.1</v>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>26.45</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>26.1</t>
+        </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
@@ -18362,7 +18430,7 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
@@ -18377,22 +18445,22 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -18587,11 +18655,15 @@
           <t>26.245</t>
         </is>
       </c>
-      <c r="CQ19" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>26.13</v>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>26.13</t>
+        </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
@@ -19344,7 +19416,7 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
@@ -19359,22 +19431,22 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
@@ -19569,11 +19641,15 @@
           <t>930.1</t>
         </is>
       </c>
-      <c r="CQ20" t="n">
-        <v>972.9</v>
-      </c>
-      <c r="CR20" t="n">
-        <v>773.01</v>
+      <c r="CQ20" t="inlineStr">
+        <is>
+          <t>972.9</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>773.01</t>
+        </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
@@ -20326,7 +20402,7 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
@@ -20341,22 +20417,22 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
@@ -20551,11 +20627,15 @@
           <t>934.5</t>
         </is>
       </c>
-      <c r="CQ21" t="n">
-        <v>977.35</v>
-      </c>
-      <c r="CR21" t="n">
-        <v>764.37</v>
+      <c r="CQ21" t="inlineStr">
+        <is>
+          <t>977.35</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>764.37</t>
+        </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
@@ -21308,7 +21388,7 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -21323,22 +21403,22 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
@@ -21533,11 +21613,15 @@
           <t>931.0</t>
         </is>
       </c>
-      <c r="CQ22" t="n">
-        <v>980.1</v>
-      </c>
-      <c r="CR22" t="n">
-        <v>755.99</v>
+      <c r="CQ22" t="inlineStr">
+        <is>
+          <t>980.1</t>
+        </is>
+      </c>
+      <c r="CR22" t="inlineStr">
+        <is>
+          <t>755.99</t>
+        </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
@@ -22280,7 +22364,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -22290,7 +22374,7 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
@@ -22305,22 +22389,22 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
@@ -22515,11 +22599,15 @@
           <t>937.4</t>
         </is>
       </c>
-      <c r="CQ23" t="n">
-        <v>985.85</v>
-      </c>
-      <c r="CR23" t="n">
-        <v>748.1900000000001</v>
+      <c r="CQ23" t="inlineStr">
+        <is>
+          <t>985.85</t>
+        </is>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>748.19</t>
+        </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
@@ -23262,7 +23350,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -23272,7 +23360,7 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
@@ -23287,22 +23375,22 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
@@ -23497,11 +23585,15 @@
           <t>955.2</t>
         </is>
       </c>
-      <c r="CQ24" t="n">
-        <v>987.6</v>
-      </c>
-      <c r="CR24" t="n">
-        <v>740.9299999999999</v>
+      <c r="CQ24" t="inlineStr">
+        <is>
+          <t>987.6</t>
+        </is>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>740.93</t>
+        </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
@@ -24244,47 +24336,47 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
@@ -24479,11 +24571,15 @@
           <t>972.1</t>
         </is>
       </c>
-      <c r="CQ25" t="n">
-        <v>984.25</v>
-      </c>
-      <c r="CR25" t="n">
-        <v>734.05</v>
+      <c r="CQ25" t="inlineStr">
+        <is>
+          <t>984.25</t>
+        </is>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
+          <t>734.05</t>
+        </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
@@ -25226,7 +25322,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -25236,7 +25332,7 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
@@ -25251,22 +25347,22 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
@@ -25461,11 +25557,15 @@
           <t>992.6</t>
         </is>
       </c>
-      <c r="CQ26" t="n">
-        <v>976.95</v>
-      </c>
-      <c r="CR26" t="n">
-        <v>727.03</v>
+      <c r="CQ26" t="inlineStr">
+        <is>
+          <t>976.95</t>
+        </is>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
+          <t>727.03</t>
+        </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
@@ -26208,7 +26308,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -26218,7 +26318,7 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -26233,22 +26333,22 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
@@ -26443,11 +26543,15 @@
           <t>1001.3</t>
         </is>
       </c>
-      <c r="CQ27" t="n">
-        <v>965.3</v>
-      </c>
-      <c r="CR27" t="n">
-        <v>720.3099999999999</v>
+      <c r="CQ27" t="inlineStr">
+        <is>
+          <t>965.3</t>
+        </is>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
+          <t>720.31</t>
+        </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
@@ -27185,12 +27289,12 @@
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -27200,7 +27304,7 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
@@ -27215,22 +27319,22 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
@@ -27425,11 +27529,15 @@
           <t>1004.8</t>
         </is>
       </c>
-      <c r="CQ28" t="n">
-        <v>950.55</v>
-      </c>
-      <c r="CR28" t="n">
-        <v>713.45</v>
+      <c r="CQ28" t="inlineStr">
+        <is>
+          <t>950.55</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
+          <t>713.45</t>
+        </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
@@ -28182,7 +28290,7 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
@@ -28197,22 +28305,22 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
@@ -28407,11 +28515,15 @@
           <t>173.65</t>
         </is>
       </c>
-      <c r="CQ29" t="n">
-        <v>179.35</v>
-      </c>
-      <c r="CR29" t="n">
-        <v>180.22</v>
+      <c r="CQ29" t="inlineStr">
+        <is>
+          <t>179.35</t>
+        </is>
+      </c>
+      <c r="CR29" t="inlineStr">
+        <is>
+          <t>180.22</t>
+        </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
@@ -29164,7 +29276,7 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
@@ -29179,22 +29291,22 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
@@ -29389,11 +29501,15 @@
           <t>173.8</t>
         </is>
       </c>
-      <c r="CQ30" t="n">
-        <v>181.08</v>
-      </c>
-      <c r="CR30" t="n">
-        <v>179.84</v>
+      <c r="CQ30" t="inlineStr">
+        <is>
+          <t>181.08</t>
+        </is>
+      </c>
+      <c r="CR30" t="inlineStr">
+        <is>
+          <t>179.84</t>
+        </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
@@ -30146,7 +30262,7 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
@@ -30161,22 +30277,22 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
@@ -30371,11 +30487,15 @@
           <t>173.05</t>
         </is>
       </c>
-      <c r="CQ31" t="n">
-        <v>182.3</v>
-      </c>
-      <c r="CR31" t="n">
-        <v>179.36</v>
+      <c r="CQ31" t="inlineStr">
+        <is>
+          <t>182.3</t>
+        </is>
+      </c>
+      <c r="CR31" t="inlineStr">
+        <is>
+          <t>179.36</t>
+        </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
@@ -31128,7 +31248,7 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
@@ -31143,22 +31263,22 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
@@ -31353,11 +31473,15 @@
           <t>172.8</t>
         </is>
       </c>
-      <c r="CQ32" t="n">
-        <v>183.85</v>
-      </c>
-      <c r="CR32" t="n">
-        <v>178.91</v>
+      <c r="CQ32" t="inlineStr">
+        <is>
+          <t>183.85</t>
+        </is>
+      </c>
+      <c r="CR32" t="inlineStr">
+        <is>
+          <t>178.91</t>
+        </is>
       </c>
       <c r="CS32" t="inlineStr">
         <is>
@@ -32110,7 +32234,7 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
@@ -32125,22 +32249,22 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
@@ -32335,11 +32459,15 @@
           <t>173.65</t>
         </is>
       </c>
-      <c r="CQ33" t="n">
-        <v>185.28</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>178.61</v>
+      <c r="CQ33" t="inlineStr">
+        <is>
+          <t>185.28</t>
+        </is>
+      </c>
+      <c r="CR33" t="inlineStr">
+        <is>
+          <t>178.61</t>
+        </is>
       </c>
       <c r="CS33" t="inlineStr">
         <is>
@@ -33092,7 +33220,7 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
@@ -33107,22 +33235,22 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
@@ -33317,11 +33445,15 @@
           <t>174.6</t>
         </is>
       </c>
-      <c r="CQ34" t="n">
-        <v>186.85</v>
-      </c>
-      <c r="CR34" t="n">
-        <v>178.54</v>
+      <c r="CQ34" t="inlineStr">
+        <is>
+          <t>186.85</t>
+        </is>
+      </c>
+      <c r="CR34" t="inlineStr">
+        <is>
+          <t>178.54</t>
+        </is>
       </c>
       <c r="CS34" t="inlineStr">
         <is>
@@ -34074,7 +34206,7 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
@@ -34089,22 +34221,22 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
@@ -34299,11 +34431,15 @@
           <t>176.55</t>
         </is>
       </c>
-      <c r="CQ35" t="n">
-        <v>188.45</v>
-      </c>
-      <c r="CR35" t="n">
-        <v>178.56</v>
+      <c r="CQ35" t="inlineStr">
+        <is>
+          <t>188.45</t>
+        </is>
+      </c>
+      <c r="CR35" t="inlineStr">
+        <is>
+          <t>178.56</t>
+        </is>
       </c>
       <c r="CS35" t="inlineStr">
         <is>
@@ -35056,7 +35192,7 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
@@ -35071,22 +35207,22 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
@@ -35281,11 +35417,15 @@
           <t>178.05</t>
         </is>
       </c>
-      <c r="CQ36" t="n">
-        <v>189.58</v>
-      </c>
-      <c r="CR36" t="n">
-        <v>178.55</v>
+      <c r="CQ36" t="inlineStr">
+        <is>
+          <t>189.58</t>
+        </is>
+      </c>
+      <c r="CR36" t="inlineStr">
+        <is>
+          <t>178.55</t>
+        </is>
       </c>
       <c r="CS36" t="inlineStr">
         <is>
@@ -36038,7 +36178,7 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
@@ -36053,22 +36193,22 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
@@ -36263,11 +36403,15 @@
           <t>179.6</t>
         </is>
       </c>
-      <c r="CQ37" t="n">
-        <v>190.28</v>
-      </c>
-      <c r="CR37" t="n">
-        <v>178.83</v>
+      <c r="CQ37" t="inlineStr">
+        <is>
+          <t>190.28</t>
+        </is>
+      </c>
+      <c r="CR37" t="inlineStr">
+        <is>
+          <t>178.83</t>
+        </is>
       </c>
       <c r="CS37" t="inlineStr">
         <is>
@@ -37020,7 +37164,7 @@
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
@@ -37035,22 +37179,22 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
@@ -37245,11 +37389,15 @@
           <t>6215.0</t>
         </is>
       </c>
-      <c r="CQ38" t="n">
-        <v>6419.25</v>
-      </c>
-      <c r="CR38" t="n">
-        <v>5639.9</v>
+      <c r="CQ38" t="inlineStr">
+        <is>
+          <t>6419.25</t>
+        </is>
+      </c>
+      <c r="CR38" t="inlineStr">
+        <is>
+          <t>5639.9</t>
+        </is>
       </c>
       <c r="CS38" t="inlineStr">
         <is>
@@ -38002,7 +38150,7 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
@@ -38017,22 +38165,22 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
@@ -38227,11 +38375,15 @@
           <t>6208.5</t>
         </is>
       </c>
-      <c r="CQ39" t="n">
-        <v>6495.25</v>
-      </c>
-      <c r="CR39" t="n">
-        <v>5594.1</v>
+      <c r="CQ39" t="inlineStr">
+        <is>
+          <t>6495.25</t>
+        </is>
+      </c>
+      <c r="CR39" t="inlineStr">
+        <is>
+          <t>5594.1</t>
+        </is>
       </c>
       <c r="CS39" t="inlineStr">
         <is>
@@ -38984,7 +39136,7 @@
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
@@ -38999,22 +39151,22 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
@@ -39209,11 +39361,15 @@
           <t>6193.5</t>
         </is>
       </c>
-      <c r="CQ40" t="n">
-        <v>6564</v>
-      </c>
-      <c r="CR40" t="n">
-        <v>5549.7</v>
+      <c r="CQ40" t="inlineStr">
+        <is>
+          <t>6564.0</t>
+        </is>
+      </c>
+      <c r="CR40" t="inlineStr">
+        <is>
+          <t>5549.7</t>
+        </is>
       </c>
       <c r="CS40" t="inlineStr">
         <is>
@@ -39966,7 +40122,7 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
@@ -39981,22 +40137,22 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
@@ -40191,11 +40347,15 @@
           <t>6198.5</t>
         </is>
       </c>
-      <c r="CQ41" t="n">
-        <v>6649.25</v>
-      </c>
-      <c r="CR41" t="n">
-        <v>5508.3</v>
+      <c r="CQ41" t="inlineStr">
+        <is>
+          <t>6649.25</t>
+        </is>
+      </c>
+      <c r="CR41" t="inlineStr">
+        <is>
+          <t>5508.3</t>
+        </is>
       </c>
       <c r="CS41" t="inlineStr">
         <is>
@@ -40948,7 +41108,7 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
@@ -40963,22 +41123,22 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
@@ -41173,11 +41333,15 @@
           <t>6262.5</t>
         </is>
       </c>
-      <c r="CQ42" t="n">
-        <v>6701.5</v>
-      </c>
-      <c r="CR42" t="n">
-        <v>5468.1</v>
+      <c r="CQ42" t="inlineStr">
+        <is>
+          <t>6701.5</t>
+        </is>
+      </c>
+      <c r="CR42" t="inlineStr">
+        <is>
+          <t>5468.1</t>
+        </is>
       </c>
       <c r="CS42" t="inlineStr">
         <is>
@@ -41930,7 +42094,7 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
@@ -41945,22 +42109,22 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
@@ -42155,11 +42319,15 @@
           <t>6310.0</t>
         </is>
       </c>
-      <c r="CQ43" t="n">
-        <v>6735</v>
-      </c>
-      <c r="CR43" t="n">
-        <v>5428.4</v>
+      <c r="CQ43" t="inlineStr">
+        <is>
+          <t>6735.0</t>
+        </is>
+      </c>
+      <c r="CR43" t="inlineStr">
+        <is>
+          <t>5428.4</t>
+        </is>
       </c>
       <c r="CS43" t="inlineStr">
         <is>
@@ -42912,7 +43080,7 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
@@ -42927,22 +43095,22 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
@@ -43137,11 +43305,15 @@
           <t>6378.0</t>
         </is>
       </c>
-      <c r="CQ44" t="n">
-        <v>6740</v>
-      </c>
-      <c r="CR44" t="n">
-        <v>5385.4</v>
+      <c r="CQ44" t="inlineStr">
+        <is>
+          <t>6740.0</t>
+        </is>
+      </c>
+      <c r="CR44" t="inlineStr">
+        <is>
+          <t>5385.4</t>
+        </is>
       </c>
       <c r="CS44" t="inlineStr">
         <is>
@@ -43894,7 +44066,7 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
@@ -43909,22 +44081,22 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
@@ -44119,11 +44291,15 @@
           <t>6387.5</t>
         </is>
       </c>
-      <c r="CQ45" t="n">
-        <v>6705.75</v>
-      </c>
-      <c r="CR45" t="n">
-        <v>5342.6</v>
+      <c r="CQ45" t="inlineStr">
+        <is>
+          <t>6705.75</t>
+        </is>
+      </c>
+      <c r="CR45" t="inlineStr">
+        <is>
+          <t>5342.6</t>
+        </is>
       </c>
       <c r="CS45" t="inlineStr">
         <is>
@@ -44866,7 +45042,7 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
@@ -44876,7 +45052,7 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
@@ -44891,22 +45067,22 @@
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
@@ -45101,11 +45277,15 @@
           <t>6413.5</t>
         </is>
       </c>
-      <c r="CQ46" t="n">
-        <v>6655</v>
-      </c>
-      <c r="CR46" t="n">
-        <v>5301.5</v>
+      <c r="CQ46" t="inlineStr">
+        <is>
+          <t>6655.0</t>
+        </is>
+      </c>
+      <c r="CR46" t="inlineStr">
+        <is>
+          <t>5301.5</t>
+        </is>
       </c>
       <c r="CS46" t="inlineStr">
         <is>
